--- a/measurements/36/Filled_2D_sections/axial/week36_axial_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/axial/week36_axial_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:AE27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,92 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,43 +586,82 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>12.65139797739441</v>
+        <v>4822.448979591836</v>
       </c>
       <c r="D2" t="n">
-        <v>40.25678338364857</v>
+        <v>785.9657708236149</v>
       </c>
       <c r="E2" t="n">
-        <v>16.66019762725365</v>
+        <v>325.2705251035236</v>
       </c>
       <c r="F2" t="n">
         <v>2.416344888838195</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0981002784693637</v>
+        <v>0.09810027846936373</v>
       </c>
       <c r="H2" t="n">
+        <v>16</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.122395833333333</v>
+      </c>
+      <c r="J2" t="n">
+        <v>43.05617559523809</v>
+      </c>
+      <c r="K2" t="n">
+        <v>10.69219680059524</v>
+      </c>
+      <c r="L2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>43.05617559523809</v>
+      </c>
+      <c r="N2" t="n">
+        <v>32.77901785714285</v>
+      </c>
+      <c r="O2" t="n">
+        <v>15.71242559523809</v>
+      </c>
+      <c r="S2" t="n">
+        <v>7</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5.293898809523809</v>
+      </c>
+      <c r="U2" t="n">
+        <v>13.1938244047619</v>
+      </c>
+      <c r="V2" t="n">
+        <v>8.857089710884352</v>
+      </c>
+      <c r="W2" t="n">
         <v>6</v>
       </c>
-      <c r="I2" t="n">
-        <v>0.5984184451219512</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2.20531631097561</v>
-      </c>
-      <c r="K2" t="n">
-        <v>1.096243013211382</v>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>2.122395833333333</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>4.66703869047619</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.921316964285714</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>12.85206722189173</v>
+      <c r="AE2" s="2" t="n">
+        <v>4898.939909297052</v>
       </c>
     </row>
     <row r="3">
@@ -553,43 +672,82 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.80606781677573</v>
+        <v>4881.40589569161</v>
       </c>
       <c r="D3" t="n">
-        <v>38.24291654912437</v>
+        <v>746.6474183400471</v>
       </c>
       <c r="E3" t="n">
-        <v>16.69714203113463</v>
+        <v>325.9918206078665</v>
       </c>
       <c r="F3" t="n">
-        <v>2.290386970285935</v>
+        <v>2.290386970285934</v>
       </c>
       <c r="G3" t="n">
         <v>0.1100331762956799</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>0.624047256097561</v>
+        <v>1.592261904761905</v>
       </c>
       <c r="J3" t="n">
-        <v>2.216177591463415</v>
+        <v>43.26822916666666</v>
       </c>
       <c r="K3" t="n">
-        <v>1.122665777439024</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>10.78985305059524</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>43.26822916666666</v>
+      </c>
+      <c r="N3" t="n">
+        <v>32.85714285714285</v>
+      </c>
+      <c r="O3" t="n">
+        <v>16.30580357142857</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>6.166294642857142</v>
+      </c>
+      <c r="U3" t="n">
+        <v>14.55357142857143</v>
+      </c>
+      <c r="V3" t="n">
+        <v>10.44010416666667</v>
+      </c>
+      <c r="W3" t="n">
+        <v>8</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.592261904761905</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>4.564732142857142</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>3.500744047619047</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>37.05383013850305</v>
+      <c r="AE3" s="2" t="n">
+        <v>723.4319217517261</v>
       </c>
     </row>
     <row r="4">
@@ -600,17 +758,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>13.12284354550863</v>
+        <v>5002.154195011338</v>
       </c>
       <c r="D4" t="n">
-        <v>39.43486918763417</v>
+        <v>769.9188746157146</v>
       </c>
       <c r="E4" t="n">
-        <v>16.75775860867849</v>
+        <v>327.1752871218181</v>
       </c>
       <c r="F4" t="n">
         <v>2.3532305309143</v>
@@ -619,24 +777,63 @@
         <v>0.1060417792446098</v>
       </c>
       <c r="H4" t="n">
+        <v>16</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.113095238095238</v>
+      </c>
+      <c r="J4" t="n">
+        <v>44.72842261904761</v>
+      </c>
+      <c r="K4" t="n">
+        <v>10.76962425595238</v>
+      </c>
+      <c r="L4" t="n">
+        <v>3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>44.72842261904761</v>
+      </c>
+      <c r="N4" t="n">
+        <v>31.12537202380952</v>
+      </c>
+      <c r="O4" t="n">
+        <v>17.47395833333333</v>
+      </c>
+      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="I4" t="n">
-        <v>0.6243330792682927</v>
-      </c>
-      <c r="J4" t="n">
-        <v>2.290967987804878</v>
-      </c>
-      <c r="K4" t="n">
-        <v>1.135035569105691</v>
-      </c>
-      <c r="N4" t="inlineStr">
+      <c r="T4" t="n">
+        <v>5.119047619047619</v>
+      </c>
+      <c r="U4" t="n">
+        <v>14.85491071428571</v>
+      </c>
+      <c r="V4" t="n">
+        <v>9.855220734126982</v>
+      </c>
+      <c r="W4" t="n">
+        <v>7</v>
+      </c>
+      <c r="X4" t="n">
+        <v>2.113095238095238</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3.995535714285714</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.83641581632653</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>16.54353061987133</v>
+      <c r="AE4" s="2" t="n">
+        <v>322.9927406736782</v>
       </c>
     </row>
     <row r="5">
@@ -647,17 +844,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>13.20107079119572</v>
+        <v>5031.972789115646</v>
       </c>
       <c r="D5" t="n">
-        <v>39.22545972103026</v>
+        <v>765.8304040772574</v>
       </c>
       <c r="E5" t="n">
-        <v>16.73755309349153</v>
+        <v>326.7807984919775</v>
       </c>
       <c r="F5" t="n">
         <v>2.343559987647373</v>
@@ -666,23 +863,62 @@
         <v>0.1078159315396223</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="I5" t="n">
-        <v>0.629954268292683</v>
+        <v>2.380952380952381</v>
       </c>
       <c r="J5" t="n">
-        <v>2.24952362804878</v>
+        <v>43.91927083333333</v>
       </c>
       <c r="K5" t="n">
-        <v>1.240948932926829</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>10.43817429315476</v>
+      </c>
+      <c r="L5" t="n">
+        <v>3</v>
+      </c>
+      <c r="M5" t="n">
+        <v>43.91927083333333</v>
+      </c>
+      <c r="N5" t="n">
+        <v>32.265625</v>
+      </c>
+      <c r="O5" t="n">
+        <v>17.98549107142857</v>
+      </c>
+      <c r="S5" t="n">
+        <v>4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.598958333333333</v>
+      </c>
+      <c r="U5" t="n">
+        <v>14.67075892857143</v>
+      </c>
+      <c r="V5" t="n">
+        <v>10.51571800595238</v>
+      </c>
+      <c r="W5" t="n">
+        <v>9</v>
+      </c>
+      <c r="X5" t="n">
+        <v>2.380952380952381</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.618675595238095</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>3.419725529100528</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="AE5" s="2" t="n">
         <v>2.239791432890807</v>
       </c>
     </row>
@@ -694,17 +930,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>13.13771564544914</v>
+        <v>5007.8231292517</v>
       </c>
       <c r="D6" t="n">
-        <v>37.38059124423236</v>
+        <v>729.8115433397746</v>
       </c>
       <c r="E6" t="n">
-        <v>16.96471667580488</v>
+        <v>331.2158970038096</v>
       </c>
       <c r="F6" t="n">
         <v>2.203431507791972</v>
@@ -713,23 +949,62 @@
         <v>0.118150996578596</v>
       </c>
       <c r="H6" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="I6" t="n">
-        <v>0.6141387195121951</v>
+        <v>1.904761904761905</v>
       </c>
       <c r="J6" t="n">
-        <v>2.172541920731708</v>
+        <v>42.41629464285714</v>
       </c>
       <c r="K6" t="n">
-        <v>1.209813262195122</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>11.49048681972789</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>42.41629464285714</v>
+      </c>
+      <c r="N6" t="n">
+        <v>31.35044642857143</v>
+      </c>
+      <c r="O6" t="n">
+        <v>18.05989583333333</v>
+      </c>
+      <c r="S6" t="n">
+        <v>4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>8.816964285714285</v>
+      </c>
+      <c r="U6" t="n">
+        <v>14.28385416666667</v>
+      </c>
+      <c r="V6" t="n">
+        <v>11.19559151785714</v>
+      </c>
+      <c r="W6" t="n">
+        <v>7</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>4.719122023809524</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3.465401785714286</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="AE6" s="2" t="n">
         <v>0.1191448305130884</v>
       </c>
     </row>
@@ -741,17 +1016,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>12.96460440214158</v>
+        <v>4941.836734693878</v>
       </c>
       <c r="D7" t="n">
-        <v>37.65509938030709</v>
+        <v>735.1709879012335</v>
       </c>
       <c r="E7" t="n">
-        <v>16.92185430410432</v>
+        <v>330.379060222989</v>
       </c>
       <c r="F7" t="n">
         <v>2.225234817863549</v>
@@ -760,24 +1035,63 @@
         <v>0.1149003990831565</v>
       </c>
       <c r="H7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.45833333333333</v>
+      </c>
+      <c r="K7" t="n">
+        <v>11.04804421768707</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>41.45833333333333</v>
+      </c>
+      <c r="N7" t="n">
+        <v>23.44122023809524</v>
+      </c>
+      <c r="O7" t="n">
+        <v>17.75483630952381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.111607142857142</v>
+      </c>
+      <c r="U7" t="n">
+        <v>14.05505952380952</v>
+      </c>
+      <c r="V7" t="n">
+        <v>10.20721726190476</v>
+      </c>
+      <c r="W7" t="n">
         <v>6</v>
       </c>
-      <c r="I7" t="n">
-        <v>0.5476371951219512</v>
-      </c>
-      <c r="J7" t="n">
-        <v>2.123475609756098</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.023643927845528</v>
-      </c>
-      <c r="N7" t="inlineStr">
+      <c r="X7" t="n">
+        <v>1.904761904761905</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>4.851190476190476</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.49702380952381</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>5.45</v>
+      <c r="AE7" s="2" t="n">
+        <v>16.75</v>
       </c>
     </row>
     <row r="8">
@@ -788,17 +1102,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.88845925044616</v>
+        <v>4912.811791383219</v>
       </c>
       <c r="D8" t="n">
-        <v>39.73101880782988</v>
+        <v>775.7008433909643</v>
       </c>
       <c r="E8" t="n">
-        <v>17.0179792817046</v>
+        <v>332.2557859761374</v>
       </c>
       <c r="F8" t="n">
         <v>2.334649616746403</v>
@@ -807,24 +1121,63 @@
         <v>0.102600969250452</v>
       </c>
       <c r="H8" t="n">
+        <v>15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.960565476190476</v>
+      </c>
+      <c r="J8" t="n">
+        <v>39.83444940476191</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10.60367063492063</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>15.33296130952381</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>39.83444940476191</v>
+      </c>
+      <c r="R8" t="n">
+        <v>23.71605282738095</v>
+      </c>
+      <c r="S8" t="n">
         <v>6</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.5667873475609756</v>
-      </c>
-      <c r="J8" t="n">
-        <v>2.040301067073171</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1.011083587398374</v>
-      </c>
-      <c r="N8" t="inlineStr">
+      <c r="T8" t="n">
+        <v>5.23251488095238</v>
+      </c>
+      <c r="U8" t="n">
+        <v>12.51116071428571</v>
+      </c>
+      <c r="V8" t="n">
+        <v>8.49516369047619</v>
+      </c>
+      <c r="W8" t="n">
+        <v>5</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.960565476190476</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3.346354166666667</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.643973214285714</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.608155487804878</v>
+      <c r="AE8" s="2" t="n">
+        <v>2.076357886904762</v>
       </c>
     </row>
     <row r="9">
@@ -835,43 +1188,82 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>12.74003569303986</v>
+        <v>4856.235827664399</v>
       </c>
       <c r="D9" t="n">
-        <v>38.05616401753775</v>
+        <v>743.0012974852607</v>
       </c>
       <c r="E9" t="n">
-        <v>17.1298277494384</v>
+        <v>334.4394941557021</v>
       </c>
       <c r="F9" t="n">
-        <v>2.221631447449051</v>
+        <v>2.22163144744905</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1105428070107311</v>
+        <v>0.1105428070107312</v>
       </c>
       <c r="H9" t="n">
+        <v>15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.215401785714286</v>
+      </c>
+      <c r="J9" t="n">
+        <v>37.99665178571428</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.83705357142857</v>
+      </c>
+      <c r="L9" t="n">
+        <v>4</v>
+      </c>
+      <c r="P9" t="n">
+        <v>16.6796875</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>37.99665178571428</v>
+      </c>
+      <c r="R9" t="n">
+        <v>24.24386160714286</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.753348214285714</v>
+      </c>
+      <c r="U9" t="n">
+        <v>12.44977678571428</v>
+      </c>
+      <c r="V9" t="n">
+        <v>9.053943452380953</v>
+      </c>
+      <c r="W9" t="n">
         <v>6</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.5466844512195123</v>
-      </c>
-      <c r="J9" t="n">
-        <v>1.946169969512195</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.025231834349594</v>
-      </c>
-      <c r="N9" t="inlineStr">
+      <c r="X9" t="n">
+        <v>2.215401785714286</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>4.306175595238095</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.385106646825397</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>1.867249428353659</v>
+      <c r="AE9" s="2" t="n">
+        <v>36.45582217261904</v>
       </c>
     </row>
     <row r="10">
@@ -882,17 +1274,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>12.6481261154075</v>
+        <v>4821.201814058956</v>
       </c>
       <c r="D10" t="n">
-        <v>39.95961839687534</v>
+        <v>780.1639782247089</v>
       </c>
       <c r="E10" t="n">
-        <v>16.72081425422575</v>
+        <v>326.4539925825028</v>
       </c>
       <c r="F10" t="n">
         <v>2.389812947463164</v>
@@ -901,24 +1293,63 @@
         <v>0.09953902603954516</v>
       </c>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5936547256097561</v>
+        <v>2.609747023809524</v>
       </c>
       <c r="J10" t="n">
-        <v>1.673875762195122</v>
+        <v>32.68043154761904</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9990631351626017</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>9.488139005602239</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17.66741071428571</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>32.68043154761904</v>
+      </c>
+      <c r="R10" t="n">
+        <v>23.4281994047619</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.871651785714286</v>
+      </c>
+      <c r="U10" t="n">
+        <v>11.72991071428571</v>
+      </c>
+      <c r="V10" t="n">
+        <v>8.296502976190476</v>
+      </c>
+      <c r="W10" t="n">
+        <v>8</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.609747023809524</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>4.672619047619047</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.262881324404762</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>1.089456210075494</v>
+      <c r="AE10" s="2" t="n">
+        <v>10.04245418933518</v>
       </c>
     </row>
     <row r="11">
@@ -929,35 +1360,82 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>12.68679357525283</v>
+        <v>4835.9410430839</v>
       </c>
       <c r="D11" t="n">
-        <v>38.28577899932861</v>
+        <v>747.4842566535586</v>
       </c>
       <c r="E11" t="n">
-        <v>16.9706347657413</v>
+        <v>331.331440664473</v>
       </c>
       <c r="F11" t="n">
-        <v>2.256001589087067</v>
+        <v>2.256001589087068</v>
       </c>
       <c r="G11" t="n">
         <v>0.1087643982531751</v>
       </c>
       <c r="H11" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6022294207317074</v>
+        <v>3.100818452380952</v>
       </c>
       <c r="J11" t="n">
-        <v>1.633669969512195</v>
+        <v>31.89546130952381</v>
       </c>
       <c r="K11" t="n">
-        <v>1.039348323170732</v>
+        <v>11.41940369897959</v>
+      </c>
+      <c r="L11" t="n">
+        <v>4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20.85193452380952</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>31.89546130952381</v>
+      </c>
+      <c r="R11" t="n">
+        <v>24.25920758928571</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="n">
+        <v>5.524553571428571</v>
+      </c>
+      <c r="U11" t="n">
+        <v>12.95758928571428</v>
+      </c>
+      <c r="V11" t="n">
+        <v>8.990699404761903</v>
+      </c>
+      <c r="W11" t="n">
+        <v>5</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3.100818452380952</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>3.833705357142857</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.57626488095238</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="AE11" s="2" t="n">
+        <v>3.35</v>
       </c>
     </row>
     <row r="12">
@@ -968,17 +1446,17 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>13.22367638310529</v>
+        <v>5040.589569160998</v>
       </c>
       <c r="D12" t="n">
-        <v>39.16137643558223</v>
+        <v>764.5792542185102</v>
       </c>
       <c r="E12" t="n">
-        <v>16.48874795146105</v>
+        <v>321.92317429043</v>
       </c>
       <c r="F12" t="n">
         <v>2.375036391535853</v>
@@ -987,16 +1465,63 @@
         <v>0.1083543074449814</v>
       </c>
       <c r="H12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6134717987804879</v>
+        <v>1.977306547619047</v>
       </c>
       <c r="J12" t="n">
-        <v>1.60718368902439</v>
+        <v>31.37834821428571</v>
       </c>
       <c r="K12" t="n">
-        <v>1.14702743902439</v>
+        <v>9.819787289915965</v>
+      </c>
+      <c r="L12" t="n">
+        <v>4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>22.27864583333333</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>31.37834821428571</v>
+      </c>
+      <c r="R12" t="n">
+        <v>24.99860491071428</v>
+      </c>
+      <c r="S12" t="n">
+        <v>7</v>
+      </c>
+      <c r="T12" t="n">
+        <v>5.385044642857142</v>
+      </c>
+      <c r="U12" t="n">
+        <v>11.97730654761905</v>
+      </c>
+      <c r="V12" t="n">
+        <v>7.065529336734692</v>
+      </c>
+      <c r="W12" t="n">
+        <v>6</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.977306547619047</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>3.852306547619047</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.913876488095238</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="AE12" s="2" t="n">
+        <v>38.53066096230158</v>
       </c>
     </row>
     <row r="13">
@@ -1007,35 +1532,82 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12.78732897085068</v>
+        <v>4874.263038548753</v>
       </c>
       <c r="D13" t="n">
-        <v>36.11229852932256</v>
+        <v>705.0496379534403</v>
       </c>
       <c r="E13" t="n">
-        <v>17.78417957119825</v>
+        <v>347.2149344852992</v>
       </c>
       <c r="F13" t="n">
-        <v>2.030585576621537</v>
+        <v>2.030585576621536</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1232194988939915</v>
+        <v>0.1232194988939916</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6034679878048781</v>
+        <v>1.834077380952381</v>
       </c>
       <c r="J13" t="n">
-        <v>1.59375</v>
+        <v>31.11607142857143</v>
       </c>
       <c r="K13" t="n">
-        <v>1.130525914634146</v>
+        <v>9.146308697089948</v>
+      </c>
+      <c r="L13" t="n">
+        <v>4</v>
+      </c>
+      <c r="P13" t="n">
+        <v>19.84933035714286</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>31.11607142857143</v>
+      </c>
+      <c r="R13" t="n">
+        <v>24.64471726190476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>4</v>
+      </c>
+      <c r="T13" t="n">
+        <v>6.060267857142857</v>
+      </c>
+      <c r="U13" t="n">
+        <v>11.78199404761905</v>
+      </c>
+      <c r="V13" t="n">
+        <v>8.295200892857142</v>
+      </c>
+      <c r="W13" t="n">
+        <v>10</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.834077380952381</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>4.769345238095238</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.287388392857142</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>29.17751736111111</v>
       </c>
     </row>
     <row r="14">
@@ -1046,17 +1618,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>12.73497917906008</v>
+        <v>4854.308390022676</v>
       </c>
       <c r="D14" t="n">
-        <v>37.6802075694247</v>
+        <v>735.6611954030536</v>
       </c>
       <c r="E14" t="n">
-        <v>17.40720777976804</v>
+        <v>339.8550090335664</v>
       </c>
       <c r="F14" t="n">
         <v>2.164632492824005</v>
@@ -1065,16 +1637,63 @@
         <v>0.1127149519457393</v>
       </c>
       <c r="H14" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>0.584032012195122</v>
+        <v>1.742931547619047</v>
       </c>
       <c r="J14" t="n">
-        <v>1.57764862804878</v>
+        <v>30.80171130952381</v>
       </c>
       <c r="K14" t="n">
-        <v>1.061043662891986</v>
+        <v>10.41744987468672</v>
+      </c>
+      <c r="L14" t="n">
+        <v>6</v>
+      </c>
+      <c r="P14" t="n">
+        <v>16.04166666666666</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>30.80171130952381</v>
+      </c>
+      <c r="R14" t="n">
+        <v>22.26779513888889</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="n">
+        <v>5.347842261904762</v>
+      </c>
+      <c r="U14" t="n">
+        <v>11.40252976190476</v>
+      </c>
+      <c r="V14" t="n">
+        <v>7.896205357142857</v>
+      </c>
+      <c r="W14" t="n">
+        <v>8</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.742931547619047</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>4.601934523809524</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.10546875</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>18.18679728835978</v>
       </c>
     </row>
     <row r="15">
@@ -1085,17 +1704,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>13.18084473527662</v>
+        <v>5024.263038548753</v>
       </c>
       <c r="D15" t="n">
-        <v>36.0290250225765</v>
+        <v>703.4238218693506</v>
       </c>
       <c r="E15" t="n">
-        <v>16.5542672785317</v>
+        <v>323.2023611522856</v>
       </c>
       <c r="F15" t="n">
         <v>2.176419192488242</v>
@@ -1104,16 +1723,63 @@
         <v>0.1275992402452977</v>
       </c>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5848894817073171</v>
+        <v>1.910342261904762</v>
       </c>
       <c r="J15" t="n">
-        <v>1.590129573170732</v>
+        <v>31.0453869047619</v>
       </c>
       <c r="K15" t="n">
-        <v>1.083955792682927</v>
+        <v>9.931175595238097</v>
+      </c>
+      <c r="L15" t="n">
+        <v>4</v>
+      </c>
+      <c r="P15" t="n">
+        <v>16.58110119047619</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>31.0453869047619</v>
+      </c>
+      <c r="R15" t="n">
+        <v>23.59886532738095</v>
+      </c>
+      <c r="S15" t="n">
+        <v>7</v>
+      </c>
+      <c r="T15" t="n">
+        <v>5.392485119047619</v>
+      </c>
+      <c r="U15" t="n">
+        <v>11.41927083333333</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.546768707482992</v>
+      </c>
+      <c r="W15" t="n">
+        <v>6</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.910342261904762</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>4.668898809523809</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.601190476190476</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>Primary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE15" s="2" t="n">
+        <v>18.16034226190476</v>
       </c>
     </row>
     <row r="16">
@@ -1124,35 +1790,82 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>13.17757287328971</v>
+        <v>5023.015873015873</v>
       </c>
       <c r="D16" t="n">
-        <v>34.74297815125163</v>
+        <v>678.3152877149128</v>
       </c>
       <c r="E16" t="n">
-        <v>16.59467832925843</v>
+        <v>323.9913388093312</v>
       </c>
       <c r="F16" t="n">
         <v>2.093621669664759</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1371864456548661</v>
+        <v>0.1371864456548662</v>
       </c>
       <c r="H16" t="n">
+        <v>17</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.53087797619047</v>
+      </c>
+      <c r="K16" t="n">
+        <v>8.501728816526608</v>
+      </c>
+      <c r="L16" t="n">
         <v>3</v>
       </c>
-      <c r="I16" t="n">
-        <v>1.058784298780488</v>
-      </c>
-      <c r="J16" t="n">
-        <v>1.61499618902439</v>
-      </c>
-      <c r="K16" t="n">
-        <v>1.33885924796748</v>
+      <c r="M16" t="n">
+        <v>31.53087797619047</v>
+      </c>
+      <c r="N16" t="n">
+        <v>26.21651785714285</v>
+      </c>
+      <c r="O16" t="n">
+        <v>20.67150297619047</v>
+      </c>
+      <c r="S16" t="n">
+        <v>6</v>
+      </c>
+      <c r="T16" t="n">
+        <v>5.537574404761904</v>
+      </c>
+      <c r="U16" t="n">
+        <v>8.755580357142856</v>
+      </c>
+      <c r="V16" t="n">
+        <v>6.960875496031746</v>
+      </c>
+      <c r="W16" t="n">
+        <v>8</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.794642857142857</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.043154761904761</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>Primary_max_mm</t>
+        </is>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>33.34356398809523</v>
       </c>
     </row>
     <row r="17">
@@ -1163,17 +1876,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12.78941106484236</v>
+        <v>4875.056689342403</v>
       </c>
       <c r="D17" t="n">
-        <v>34.7705377485694</v>
+        <v>678.8533560434977</v>
       </c>
       <c r="E17" t="n">
-        <v>15.64172547038009</v>
+        <v>305.3860687074207</v>
       </c>
       <c r="F17" t="n">
         <v>2.222934919450705</v>
@@ -1182,16 +1895,63 @@
         <v>0.1329344660595747</v>
       </c>
       <c r="H17" t="n">
+        <v>17</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="J17" t="n">
+        <v>32.46465773809523</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.365918242296916</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>32.46465773809523</v>
+      </c>
+      <c r="N17" t="n">
+        <v>25.5078125</v>
+      </c>
+      <c r="O17" t="n">
+        <v>20.17299107142857</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.992559523809524</v>
+      </c>
+      <c r="U17" t="n">
+        <v>12.86272321428571</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.058221726190476</v>
+      </c>
+      <c r="W17" t="n">
         <v>4</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.6588224085365854</v>
-      </c>
-      <c r="J17" t="n">
-        <v>1.662823932926829</v>
-      </c>
-      <c r="K17" t="n">
-        <v>1.165348704268293</v>
+      <c r="X17" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>3.145461309523809</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.623232886904762</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>Primary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AE17" s="2" t="n">
+        <v>23.89466300843254</v>
       </c>
     </row>
     <row r="18">
@@ -1202,17 +1962,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>12.49494348602023</v>
+        <v>4762.811791383219</v>
       </c>
       <c r="D18" t="n">
-        <v>34.38172980924932</v>
+        <v>671.2623438948676</v>
       </c>
       <c r="E18" t="n">
-        <v>15.63825874503066</v>
+        <v>305.3183850220271</v>
       </c>
       <c r="F18" t="n">
         <v>2.198565094094938</v>
@@ -1221,16 +1981,63 @@
         <v>0.1328277187929027</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5022865853658537</v>
+        <v>2.129836309523809</v>
       </c>
       <c r="J18" t="n">
-        <v>1.705887957317073</v>
+        <v>33.30543154761904</v>
       </c>
       <c r="K18" t="n">
-        <v>1.032393292682927</v>
+        <v>8.737272869674186</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>33.30543154761904</v>
+      </c>
+      <c r="N18" t="n">
+        <v>25.61941964285714</v>
+      </c>
+      <c r="O18" t="n">
+        <v>19.54427083333333</v>
+      </c>
+      <c r="S18" t="n">
+        <v>8</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4.799107142857142</v>
+      </c>
+      <c r="U18" t="n">
+        <v>12.50558035714286</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7.121930803571429</v>
+      </c>
+      <c r="W18" t="n">
+        <v>8</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>4.663318452380953</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.820452008928571</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="AE18" s="2" t="n">
+        <v>6.55</v>
       </c>
     </row>
     <row r="19">
@@ -1241,35 +2048,79 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>12.75936942296252</v>
+        <v>4863.60544217687</v>
       </c>
       <c r="D19" t="n">
-        <v>31.90330968833551</v>
+        <v>622.8741415341694</v>
       </c>
       <c r="E19" t="n">
-        <v>15.67275174361903</v>
+        <v>305.9918197563716</v>
       </c>
       <c r="F19" t="n">
         <v>2.035590827330277</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1575315682626235</v>
+        <v>0.1575315682626236</v>
       </c>
       <c r="H19" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="I19" t="n">
-        <v>0.5413490853658537</v>
+        <v>1.837797619047619</v>
       </c>
       <c r="J19" t="n">
-        <v>1.752286585365854</v>
+        <v>34.21130952380952</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8991679369918698</v>
+        <v>8.287946428571427</v>
+      </c>
+      <c r="L19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M19" t="n">
+        <v>34.21130952380952</v>
+      </c>
+      <c r="N19" t="n">
+        <v>25.55059523809524</v>
+      </c>
+      <c r="S19" t="n">
+        <v>9</v>
+      </c>
+      <c r="T19" t="n">
+        <v>4.713541666666666</v>
+      </c>
+      <c r="U19" t="n">
+        <v>12.70647321428571</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.526372354497354</v>
+      </c>
+      <c r="W19" t="n">
+        <v>9</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.837797619047619</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>4.29501488095238</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.251074735449736</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>Secondary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>5.453031994047619</v>
       </c>
     </row>
     <row r="20">
@@ -1280,17 +2131,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12.66537775133849</v>
+        <v>4827.777777777777</v>
       </c>
       <c r="D20" t="n">
-        <v>32.35070354182546</v>
+        <v>631.6089739118303</v>
       </c>
       <c r="E20" t="n">
-        <v>15.38843822188494</v>
+        <v>300.4409367129916</v>
       </c>
       <c r="F20" t="n">
         <v>2.102273348039786</v>
@@ -1299,16 +2150,60 @@
         <v>0.1520759547451498</v>
       </c>
       <c r="H20" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5529725609756098</v>
+        <v>2.129836309523809</v>
       </c>
       <c r="J20" t="n">
-        <v>1.809260670731707</v>
+        <v>35.32366071428572</v>
       </c>
       <c r="K20" t="n">
-        <v>1.007907774390244</v>
+        <v>8.858376409774433</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M20" t="n">
+        <v>35.32366071428572</v>
+      </c>
+      <c r="N20" t="n">
+        <v>28.97321428571428</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="n">
+        <v>4.713541666666666</v>
+      </c>
+      <c r="U20" t="n">
+        <v>12.45907738095238</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8.121837797619047</v>
+      </c>
+      <c r="W20" t="n">
+        <v>7</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.129836309523809</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>4.045758928571428</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.256271258503401</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>Secondary_max_mm</t>
+        </is>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>12.71019345238095</v>
       </c>
     </row>
     <row r="21">
@@ -1319,35 +2214,79 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>axial</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>12.3807257584771</v>
+        <v>4719.274376417233</v>
       </c>
       <c r="D21" t="n">
-        <v>35.71613658637536</v>
+        <v>697.3150476387568</v>
       </c>
       <c r="E21" t="n">
-        <v>15.12187891471677</v>
+        <v>295.2366835730416</v>
       </c>
       <c r="F21" t="n">
-        <v>2.361884841679036</v>
+        <v>2.361884841679035</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1219626964517099</v>
+        <v>0.12196269645171</v>
       </c>
       <c r="H21" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5151486280487805</v>
+        <v>2.442336309523809</v>
       </c>
       <c r="J21" t="n">
-        <v>1.879001524390244</v>
+        <v>36.68526785714285</v>
       </c>
       <c r="K21" t="n">
-        <v>1.019817073170732</v>
+        <v>10.20647321428571</v>
+      </c>
+      <c r="L21" t="n">
+        <v>2</v>
+      </c>
+      <c r="M21" t="n">
+        <v>36.68526785714285</v>
+      </c>
+      <c r="N21" t="n">
+        <v>34.44382440476191</v>
+      </c>
+      <c r="S21" t="n">
+        <v>13</v>
+      </c>
+      <c r="T21" t="n">
+        <v>4.629836309523809</v>
+      </c>
+      <c r="U21" t="n">
+        <v>13.07291666666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.548964056776557</v>
+      </c>
+      <c r="W21" t="n">
+        <v>4</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.442336309523809</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3.642113095238095</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.914341517857143</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>Secondary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AE21" s="2" t="n">
+        <v>8.652457872505305</v>
       </c>
     </row>
     <row r="22">
@@ -1357,7 +2296,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>6.85</v>
       </c>
     </row>
     <row r="23">
@@ -1371,6 +2318,14 @@
           <t>mm</t>
         </is>
       </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Tertiary_min_mm</t>
+        </is>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>2.076357886904762</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1380,6 +2335,62 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Tertiary_max_mm</t>
+        </is>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>4.252697172619047</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>Tertiary_mean_mm</t>
+        </is>
+      </c>
+      <c r="AE25" s="2" t="n">
+        <v>3.21626526478647</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/36/Filled_2D_sections/axial/week36_axial_Batch_Allmarks.xlsx
+++ b/measurements/36/Filled_2D_sections/axial/week36_axial_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2396,4 +2602,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week36_axial_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>axial</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4898.939909297052</v>
+      </c>
+      <c r="D10" t="n">
+        <v>95.06034022167479</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4719.274376417233</v>
+      </c>
+      <c r="F10" t="n">
+        <v>5040.589569160998</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>723.4319217517262</v>
+      </c>
+      <c r="D11" t="n">
+        <v>48.14964784686919</v>
+      </c>
+      <c r="E11" t="n">
+        <v>622.8741415341694</v>
+      </c>
+      <c r="F11" t="n">
+        <v>785.9657708236149</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>2.239791432890807</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1173359676712181</v>
+      </c>
+      <c r="E12" t="n">
+        <v>2.030585576621536</v>
+      </c>
+      <c r="F12" t="n">
+        <v>2.416344888838195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.1191448305130885</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01654251669776244</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.09810027846936373</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1575315682626236</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis2_s00_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>7</v>
+      </c>
+      <c r="E17" t="n">
+        <v>6</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>6</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis2_s01_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>16</v>
+      </c>
+      <c r="H18" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" t="n">
+        <v>5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis2_s02_idx0139.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>6</v>
+      </c>
+      <c r="E19" t="n">
+        <v>7</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>16</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>6</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis2_s03_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4</v>
+      </c>
+      <c r="E20" t="n">
+        <v>9</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>16</v>
+      </c>
+      <c r="H20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="n">
+        <v>9</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis2_s04_idx0143.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>14</v>
+      </c>
+      <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>7</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis2_s05_idx0145.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
+        <v>6</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>14</v>
+      </c>
+      <c r="H22" t="n">
+        <v>3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis2_s06_idx0147.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>15</v>
+      </c>
+      <c r="C23" t="n">
+        <v>4</v>
+      </c>
+      <c r="D23" t="n">
+        <v>6</v>
+      </c>
+      <c r="E23" t="n">
+        <v>5</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" t="n">
+        <v>6</v>
+      </c>
+      <c r="J23" t="n">
+        <v>5</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis2_s07_idx0149.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>15</v>
+      </c>
+      <c r="C24" t="n">
+        <v>4</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
+        <v>6</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" t="n">
+        <v>4</v>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="n">
+        <v>6</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis2_s08_idx0151.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>17</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
+        <v>8</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>17</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4</v>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="n">
+        <v>8</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis2_s09_idx0153.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>14</v>
+      </c>
+      <c r="C26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>14</v>
+      </c>
+      <c r="H26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I26" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis2_s10_idx0156.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>17</v>
+      </c>
+      <c r="C27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D27" t="n">
+        <v>7</v>
+      </c>
+      <c r="E27" t="n">
+        <v>6</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>17</v>
+      </c>
+      <c r="H27" t="n">
+        <v>4</v>
+      </c>
+      <c r="I27" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis2_s11_idx0158.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>18</v>
+      </c>
+      <c r="C28" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" t="n">
+        <v>4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>10</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>18</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4</v>
+      </c>
+      <c r="I28" t="n">
+        <v>4</v>
+      </c>
+      <c r="J28" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis2_s12_idx0160.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>19</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>19</v>
+      </c>
+      <c r="H29" t="n">
+        <v>6</v>
+      </c>
+      <c r="I29" t="n">
+        <v>5</v>
+      </c>
+      <c r="J29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis2_s13_idx0162.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>17</v>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>7</v>
+      </c>
+      <c r="E30" t="n">
+        <v>6</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>7</v>
+      </c>
+      <c r="J30" t="n">
+        <v>6</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis2_s14_idx0164.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>17</v>
+      </c>
+      <c r="C31" t="n">
+        <v>3</v>
+      </c>
+      <c r="D31" t="n">
+        <v>6</v>
+      </c>
+      <c r="E31" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>17</v>
+      </c>
+      <c r="H31" t="n">
+        <v>3</v>
+      </c>
+      <c r="I31" t="n">
+        <v>6</v>
+      </c>
+      <c r="J31" t="n">
+        <v>8</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis2_s15_idx0166.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>17</v>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="n">
+        <v>4</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>17</v>
+      </c>
+      <c r="H32" t="n">
+        <v>3</v>
+      </c>
+      <c r="I32" t="n">
+        <v>10</v>
+      </c>
+      <c r="J32" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis2_s16_idx0168.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>19</v>
+      </c>
+      <c r="C33" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" t="n">
+        <v>8</v>
+      </c>
+      <c r="E33" t="n">
+        <v>8</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>19</v>
+      </c>
+      <c r="H33" t="n">
+        <v>3</v>
+      </c>
+      <c r="I33" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis2_s17_idx0170.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>20</v>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="n">
+        <v>9</v>
+      </c>
+      <c r="E34" t="n">
+        <v>9</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" t="n">
+        <v>2</v>
+      </c>
+      <c r="I34" t="n">
+        <v>9</v>
+      </c>
+      <c r="J34" t="n">
+        <v>9</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis2_s18_idx0172.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>19</v>
+      </c>
+      <c r="C35" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="n">
+        <v>7</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>19</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2</v>
+      </c>
+      <c r="I35" t="n">
+        <v>10</v>
+      </c>
+      <c r="J35" t="n">
+        <v>7</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis2_s19_idx0174.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>19</v>
+      </c>
+      <c r="C36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>13</v>
+      </c>
+      <c r="E36" t="n">
+        <v>4</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>19</v>
+      </c>
+      <c r="H36" t="n">
+        <v>2</v>
+      </c>
+      <c r="I36" t="n">
+        <v>13</v>
+      </c>
+      <c r="J36" t="n">
+        <v>4</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>16.75</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1.831737742662616</v>
+      </c>
+      <c r="E40" t="n">
+        <v>14</v>
+      </c>
+      <c r="F40" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.9333020044867296</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2.394621165511528</v>
+      </c>
+      <c r="E42" t="n">
+        <v>4</v>
+      </c>
+      <c r="F42" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>6.85</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.663066286617648</v>
+      </c>
+      <c r="E43" t="n">
+        <v>4</v>
+      </c>
+      <c r="F43" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>67</v>
+      </c>
+      <c r="C48" t="n">
+        <v>26.64692719438521</v>
+      </c>
+      <c r="D48" t="n">
+        <v>8.108837792036542</v>
+      </c>
+      <c r="E48" t="n">
+        <v>15.33296130952381</v>
+      </c>
+      <c r="F48" t="n">
+        <v>44.72842261904761</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>131</v>
+      </c>
+      <c r="C49" t="n">
+        <v>8.452309955470737</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2.396729779280727</v>
+      </c>
+      <c r="E49" t="n">
+        <v>4.629836309523809</v>
+      </c>
+      <c r="F49" t="n">
+        <v>14.85491071428571</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>137</v>
+      </c>
+      <c r="C50" t="n">
+        <v>3.24702109402155</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.7037442489141905</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.488095238095238</v>
+      </c>
+      <c r="F50" t="n">
+        <v>4.851190476190476</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>